--- a/output/pdf_financials_xlsx/RUSH.xlsx
+++ b/output/pdf_financials_xlsx/RUSH.xlsx
@@ -5462,16 +5462,16 @@
         <v>2.006806</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>2.035371</v>
+        <v>2.336084</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>2.035371</v>
+        <v>2.336084</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>2.202904</v>
+        <v>2.497816</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>2.829995</v>
+        <v>2.912878</v>
       </c>
       <c r="H92" s="3" t="n">
         <v>2.829995</v>
@@ -14473,7 +14473,11 @@
           <t>Warrant reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -15660,7 +15664,11 @@
           <t>Warrant reserve (Note 9) 427,848</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -16376,7 +16384,11 @@
           <t>Warrant reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -17377,7 +17389,11 @@
           <t>Warrant reserve (Note 10) 300,713</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/RUSH.xlsx
+++ b/output/pdf_financials_xlsx/RUSH.xlsx
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.07971</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.006703</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001132</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.051146</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.003359</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.003512</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1059,13 +1059,13 @@
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.048849</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.007386</v>
       </c>
     </row>
     <row r="13">
@@ -1889,22 +1889,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.633901</v>
+        <v>-0.713611</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.58323</v>
+        <v>-0.589933</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.482102</v>
+        <v>-0.483234</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.322036</v>
+        <v>-0.373182</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.441477</v>
+        <v>-0.444836</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-8.240625</v>
+        <v>-8.244137</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>0.9774040000000001</v>
@@ -1925,13 +1925,13 @@
         <v>-2.337892</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-1.992074</v>
+        <v>-1.995074</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-2.688111</v>
+        <v>-2.73696</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-1.468839</v>
+        <v>-1.476225</v>
       </c>
     </row>
     <row r="28">
@@ -1993,22 +1993,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.633901</v>
+        <v>-0.713611</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.58323</v>
+        <v>-0.589933</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.482102</v>
+        <v>-0.483234</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.322036</v>
+        <v>-0.373182</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.441477</v>
+        <v>-0.444836</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-8.240625</v>
+        <v>-8.244137</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>0.9774040000000001</v>
@@ -2029,13 +2029,13 @@
         <v>-2.337892</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.992074</v>
+        <v>-1.995074</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-2.688111</v>
+        <v>-2.73696</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-1.468839</v>
+        <v>-1.476225</v>
       </c>
     </row>
     <row r="30">
@@ -2268,37 +2268,37 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.279377</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.279377</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.286255</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.218105</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.11784</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.014997</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.014997</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.630676</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.06118</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.72598</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.224808</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>0.264774</v>
@@ -2372,37 +2372,37 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.279377</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.279377</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.286255</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.218105</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.11784</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.014997</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.014997</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.630676</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.06118</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.72598</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.224808</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>0.264774</v>
@@ -2996,37 +2996,37 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>3.29769</v>
+        <v>3.018313</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.29769</v>
+        <v>3.018313</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.219754</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.218245</v>
+        <v>0.00014</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.11798</v>
+        <v>0.00014</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.014997</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.01508</v>
+        <v>8.3e-05</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.700897</v>
+        <v>0.07022100000000001</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.085399</v>
+        <v>0.024219</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.797938</v>
+        <v>0.07195799999999999</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.252246</v>
+        <v>0.027438</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0.043985</v>
@@ -8346,7 +8346,11 @@
           <t>Reclamation deposit (note 10)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -10060,7 +10064,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
@@ -12382,7 +12386,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -14661,7 +14665,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -16568,7 +16572,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -19254,7 +19258,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -31867,7 +31875,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -32846,7 +32854,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -34185,7 +34193,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -36867,7 +36875,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -37504,7 +37512,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -38402,7 +38410,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -40058,7 +40066,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E361" s="5" t="n">

--- a/output/pdf_financials_xlsx/RUSH.xlsx
+++ b/output/pdf_financials_xlsx/RUSH.xlsx
@@ -1569,7 +1569,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0</v>
+        <v>1.370311</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>0</v>
@@ -4091,16 +4091,16 @@
         <v>0</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.037554</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.08937199999999999</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.042949</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.046335</v>
       </c>
     </row>
     <row r="68">
@@ -24526,7 +24526,11 @@
           <t>Units issued by private placement</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -36420,7 +36424,11 @@
           <t>Income from discontinued operations (Note 18)</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
